--- a/sheets/대금율보/검수/약속.xlsx
+++ b/sheets/대금율보/검수/약속.xlsx
@@ -8576,23 +8576,11 @@
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
@@ -8787,11 +8775,7 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B7" s="21"/>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
@@ -8922,23 +8906,11 @@
         </is>
       </c>
       <c r="O8" s="26"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="24"/>
-      <c r="T8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -9054,29 +9026,13 @@
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -9287,17 +9243,9 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="23"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
@@ -9423,31 +9371,24 @@
           <t xml:space="preserve">사연</t>
         </is>
       </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="S14" s="24"/>
       <c r="T14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="U14" s="24"/>
@@ -9581,11 +9522,7 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="23"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -9636,17 +9573,9 @@
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="P18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R18" s="21"/>
       <c r="S18" s="23"/>
       <c r="T18" s="21" t="inlineStr">
         <is>
@@ -9874,29 +9803,13 @@
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="23"/>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H21" s="21"/>
       <c r="I21" s="23"/>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J21" s="21"/>
       <c r="K21" s="23"/>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L21" s="21"/>
       <c r="M21" s="23"/>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N21" s="21"/>
       <c r="O21" s="23"/>
       <c r="P21" s="21" t="inlineStr">
         <is>
@@ -10109,17 +10022,9 @@
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D24" s="21"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F24" s="21"/>
       <c r="G24" s="23"/>
       <c r="H24" s="21" t="inlineStr">
         <is>
@@ -10163,11 +10068,7 @@
       </c>
       <c r="P24" s="21"/>
       <c r="Q24" s="23"/>
-      <c r="R24" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R24" s="21"/>
       <c r="S24" s="23"/>
       <c r="T24" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/약속.xlsx
+++ b/sheets/대금율보/검수/약속.xlsx
@@ -8430,32 +8430,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -9393,10 +9393,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -9835,7 +9835,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -10018,7 +10018,7 @@
       <c r="T23" s="21"/>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -10312,7 +10312,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -10413,7 +10413,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
